--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754912235_h_7.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754912235_h_7.xlsx
@@ -658,7 +658,7 @@
         <v>0.008438437034621818</v>
       </c>
       <c r="C2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>31652307</v>
+        <v>4138344</v>
       </c>
       <c r="L2" t="n">
-        <v>17933273</v>
+        <v>2074965</v>
       </c>
       <c r="M2" t="n">
-        <v>4229552</v>
+        <v>454230</v>
       </c>
       <c r="N2" t="n">
-        <v>181418</v>
+        <v>14682</v>
       </c>
       <c r="O2" t="n">
-        <v>2462892</v>
+        <v>266624</v>
       </c>
       <c r="P2" t="n">
-        <v>989729</v>
+        <v>113578</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9998973608016968</v>
+        <v>0.9999027252197266</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8841572999954224</v>
+        <v>0.8026859760284424</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7735888957977295</v>
+        <v>0.6309080123901367</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7175775170326233</v>
+        <v>0.5358033776283264</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2178509533405304</v>
+        <v>0.1214743703603745</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7619296908378601</v>
+        <v>0.6010473370552063</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8451399207115173</v>
+        <v>0.7129191160202026</v>
       </c>
       <c r="X2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>33659447</v>
+        <v>4787035</v>
       </c>
       <c r="AG2" t="n">
-        <v>20826834</v>
+        <v>2990204</v>
       </c>
       <c r="AH2" t="n">
-        <v>5601637</v>
+        <v>802709</v>
       </c>
       <c r="AI2" t="n">
-        <v>413079</v>
+        <v>59088</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3215114</v>
+        <v>460006</v>
       </c>
       <c r="AK2" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9563413858413696</v>
+        <v>0.9555707573890686</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113937020301819</v>
+        <v>0.9118538498878479</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582093119621277</v>
+        <v>0.8584820032119751</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6620789766311646</v>
+        <v>0.6613538861274719</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020217657089233</v>
+        <v>0.9020804166793823</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.931441068649292</v>
+        <v>0.9314774870872498</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.00202340465893989</v>
       </c>
       <c r="C3" t="n">
-        <v>1421</v>
+        <v>209</v>
       </c>
       <c r="D3" t="n">
-        <v>31652307</v>
+        <v>4138344</v>
       </c>
       <c r="E3" t="n">
-        <v>3422343</v>
+        <v>831401</v>
       </c>
       <c r="F3" t="n">
-        <v>64729</v>
+        <v>25285</v>
       </c>
       <c r="G3" t="n">
-        <v>6807</v>
+        <v>2248</v>
       </c>
       <c r="H3" t="n">
-        <v>3493</v>
+        <v>1556</v>
       </c>
       <c r="I3" t="n">
-        <v>189</v>
+        <v>98</v>
       </c>
       <c r="J3" t="n">
-        <v>70111818</v>
+        <v>10016008</v>
       </c>
       <c r="K3" t="n">
-        <v>75008810</v>
+        <v>10313183</v>
       </c>
       <c r="L3" t="n">
-        <v>86170604</v>
+        <v>11828191</v>
       </c>
       <c r="M3" t="n">
-        <v>106109665</v>
+        <v>14999526</v>
       </c>
       <c r="N3" t="n">
-        <v>113031401</v>
+        <v>16133953</v>
       </c>
       <c r="O3" t="n">
-        <v>109971405</v>
+        <v>15642183</v>
       </c>
       <c r="P3" t="n">
-        <v>112772314</v>
+        <v>16090357</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.900459349155426</v>
+        <v>0.8278110027313232</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7835245728492737</v>
+        <v>0.6311644315719604</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6474255323410034</v>
+        <v>0.4850039780139923</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2905221283435822</v>
+        <v>0.1641107052564621</v>
       </c>
       <c r="V3" t="n">
-        <v>0.690611720085144</v>
+        <v>0.5223394632339478</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7312195301055908</v>
+        <v>0.5869451761245728</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>33659447</v>
+        <v>4787035</v>
       </c>
       <c r="Z3" t="n">
-        <v>1384204</v>
+        <v>196812</v>
       </c>
       <c r="AA3" t="n">
-        <v>59560</v>
+        <v>8425</v>
       </c>
       <c r="AB3" t="n">
-        <v>47621</v>
+        <v>6828</v>
       </c>
       <c r="AC3" t="n">
-        <v>247</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>70116354</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>77619300</v>
+        <v>11107886</v>
       </c>
       <c r="AG3" t="n">
-        <v>89394449</v>
+        <v>12753027</v>
       </c>
       <c r="AH3" t="n">
-        <v>106848837</v>
+        <v>15260727</v>
       </c>
       <c r="AI3" t="n">
-        <v>113471912</v>
+        <v>16209880</v>
       </c>
       <c r="AJ3" t="n">
-        <v>110391725</v>
+        <v>15769225</v>
       </c>
       <c r="AK3" t="n">
-        <v>112860888</v>
+        <v>16122838</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575594067573547</v>
+        <v>0.9575715065002441</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099474549293518</v>
+        <v>0.9095625281333923</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8574531674385071</v>
+        <v>0.8570923805236816</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6615032553672791</v>
+        <v>0.6604667901992798</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015399217605591</v>
+        <v>0.9011915326118469</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312731623649597</v>
+        <v>0.9311549663543701</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03193072151668488</v>
       </c>
       <c r="C4" t="n">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="D4" t="n">
-        <v>3891182</v>
+        <v>950299</v>
       </c>
       <c r="E4" t="n">
-        <v>17933273</v>
+        <v>2074965</v>
       </c>
       <c r="F4" t="n">
-        <v>940297</v>
+        <v>219717</v>
       </c>
       <c r="G4" t="n">
-        <v>48321</v>
+        <v>14802</v>
       </c>
       <c r="H4" t="n">
-        <v>68079</v>
+        <v>24870</v>
       </c>
       <c r="I4" t="n">
-        <v>6653</v>
+        <v>2821</v>
       </c>
       <c r="J4" t="n">
-        <v>4536</v>
+        <v>614</v>
       </c>
       <c r="K4" t="n">
-        <v>4147101</v>
+        <v>1017276</v>
       </c>
       <c r="L4" t="n">
-        <v>5248643</v>
+        <v>1213890</v>
       </c>
       <c r="M4" t="n">
-        <v>1664657</v>
+        <v>393525</v>
       </c>
       <c r="N4" t="n">
-        <v>651344</v>
+        <v>106183</v>
       </c>
       <c r="O4" t="n">
-        <v>769548</v>
+        <v>176975</v>
       </c>
       <c r="P4" t="n">
-        <v>181354</v>
+        <v>45736</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999486804008484</v>
+        <v>0.9999513626098633</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8922338485717773</v>
+        <v>0.8150548934936523</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7785250544548035</v>
+        <v>0.6310362219810486</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6806988120079041</v>
+        <v>0.5091396570205688</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2489924132823944</v>
+        <v>0.1396098434925079</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7245199084281921</v>
+        <v>0.5589361190795898</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7840632796287537</v>
+        <v>0.6438278555870056</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1434717</v>
+        <v>207948</v>
       </c>
       <c r="Z4" t="n">
-        <v>20826834</v>
+        <v>2990204</v>
       </c>
       <c r="AA4" t="n">
-        <v>579437</v>
+        <v>82633</v>
       </c>
       <c r="AB4" t="n">
-        <v>38501</v>
+        <v>5536</v>
       </c>
       <c r="AC4" t="n">
-        <v>7988</v>
+        <v>1130</v>
       </c>
       <c r="AD4" t="n">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1536611</v>
+        <v>222573</v>
       </c>
       <c r="AG4" t="n">
-        <v>2024798</v>
+        <v>289054</v>
       </c>
       <c r="AH4" t="n">
-        <v>925485</v>
+        <v>132324</v>
       </c>
       <c r="AI4" t="n">
-        <v>210833</v>
+        <v>30256</v>
       </c>
       <c r="AJ4" t="n">
-        <v>349228</v>
+        <v>49933</v>
       </c>
       <c r="AK4" t="n">
-        <v>92780</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9569499492645264</v>
+        <v>0.9565700888633728</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106699824333191</v>
+        <v>0.9107067584991455</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578310608863831</v>
+        <v>0.8577865958213806</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6617910265922546</v>
+        <v>0.6609100103378296</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017807841300964</v>
+        <v>0.9016357064247131</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313570857048035</v>
+        <v>0.9313161373138428</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1335</v>
+        <v>200</v>
       </c>
       <c r="D5" t="n">
-        <v>169075</v>
+        <v>47651</v>
       </c>
       <c r="E5" t="n">
-        <v>1551677</v>
+        <v>311447</v>
       </c>
       <c r="F5" t="n">
-        <v>4229552</v>
+        <v>454230</v>
       </c>
       <c r="G5" t="n">
-        <v>228820</v>
+        <v>34371</v>
       </c>
       <c r="H5" t="n">
-        <v>321578</v>
+        <v>78046</v>
       </c>
       <c r="I5" t="n">
-        <v>30841</v>
+        <v>10604</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3498982</v>
+        <v>860797</v>
       </c>
       <c r="L5" t="n">
-        <v>4954680</v>
+        <v>1212554</v>
       </c>
       <c r="M5" t="n">
-        <v>2303326</v>
+        <v>482319</v>
       </c>
       <c r="N5" t="n">
-        <v>443037</v>
+        <v>74782</v>
       </c>
       <c r="O5" t="n">
-        <v>1103355</v>
+        <v>243818</v>
       </c>
       <c r="P5" t="n">
-        <v>363803</v>
+        <v>79929</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999603033065796</v>
+        <v>0.9999623894691467</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9331093430519104</v>
+        <v>0.8849896788597107</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9107376933097839</v>
+        <v>0.8514082431793213</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9652866721153259</v>
+        <v>0.9463646411895752</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9904259443283081</v>
+        <v>0.9889180064201355</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9836151599884033</v>
+        <v>0.9742313027381897</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9952307939529419</v>
+        <v>0.9923044443130493</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>56186</v>
+        <v>8031</v>
       </c>
       <c r="Z5" t="n">
-        <v>596891</v>
+        <v>86001</v>
       </c>
       <c r="AA5" t="n">
-        <v>5601637</v>
+        <v>802709</v>
       </c>
       <c r="AB5" t="n">
-        <v>69704</v>
+        <v>9990</v>
       </c>
       <c r="AC5" t="n">
-        <v>204029</v>
+        <v>29185</v>
       </c>
       <c r="AD5" t="n">
-        <v>4431</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1491842</v>
+        <v>212106</v>
       </c>
       <c r="AG5" t="n">
-        <v>2061119</v>
+        <v>297315</v>
       </c>
       <c r="AH5" t="n">
-        <v>931241</v>
+        <v>133840</v>
       </c>
       <c r="AI5" t="n">
-        <v>211376</v>
+        <v>30376</v>
       </c>
       <c r="AJ5" t="n">
-        <v>351133</v>
+        <v>50436</v>
       </c>
       <c r="AK5" t="n">
-        <v>93024</v>
+        <v>13322</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735060334205627</v>
+        <v>0.9733809232711792</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642549753189087</v>
+        <v>0.9640916585922241</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837567210197449</v>
+        <v>0.9837005138397217</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963063597679138</v>
+        <v>0.9962869882583618</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938730001449585</v>
+        <v>0.9938535690307617</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983745217323303</v>
+        <v>0.9983724355697632</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>248</v>
+        <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>81817</v>
+        <v>16314</v>
       </c>
       <c r="E6" t="n">
-        <v>143156</v>
+        <v>22257</v>
       </c>
       <c r="F6" t="n">
-        <v>149603</v>
+        <v>24691</v>
       </c>
       <c r="G6" t="n">
-        <v>181418</v>
+        <v>14682</v>
       </c>
       <c r="H6" t="n">
-        <v>63163</v>
+        <v>10108</v>
       </c>
       <c r="I6" t="n">
-        <v>5050</v>
+        <v>1378</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>45337</v>
+        <v>6558</v>
       </c>
       <c r="Z6" t="n">
-        <v>37466</v>
+        <v>5350</v>
       </c>
       <c r="AA6" t="n">
-        <v>76329</v>
+        <v>10994</v>
       </c>
       <c r="AB6" t="n">
-        <v>413079</v>
+        <v>59088</v>
       </c>
       <c r="AC6" t="n">
-        <v>48877</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>3367</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>278</v>
+        <v>35</v>
       </c>
       <c r="D7" t="n">
-        <v>4746</v>
+        <v>2931</v>
       </c>
       <c r="E7" t="n">
-        <v>123253</v>
+        <v>44993</v>
       </c>
       <c r="F7" t="n">
-        <v>486099</v>
+        <v>115245</v>
       </c>
       <c r="G7" t="n">
-        <v>350358</v>
+        <v>49779</v>
       </c>
       <c r="H7" t="n">
-        <v>2462892</v>
+        <v>266624</v>
       </c>
       <c r="I7" t="n">
-        <v>138621</v>
+        <v>30835</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>175</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>5670</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>207844</v>
+        <v>29939</v>
       </c>
       <c r="AB7" t="n">
-        <v>53148</v>
+        <v>7636</v>
       </c>
       <c r="AC7" t="n">
-        <v>3215114</v>
+        <v>460006</v>
       </c>
       <c r="AD7" t="n">
-        <v>84296</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1106</v>
+        <v>91</v>
       </c>
       <c r="D8" t="n">
-        <v>281</v>
+        <v>81</v>
       </c>
       <c r="E8" t="n">
-        <v>8214</v>
+        <v>3792</v>
       </c>
       <c r="F8" t="n">
-        <v>23929</v>
+        <v>8587</v>
       </c>
       <c r="G8" t="n">
-        <v>17038</v>
+        <v>4983</v>
       </c>
       <c r="H8" t="n">
-        <v>313235</v>
+        <v>62395</v>
       </c>
       <c r="I8" t="n">
-        <v>989729</v>
+        <v>113578</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>567</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2315</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>1859</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>88087</v>
+        <v>12614</v>
       </c>
       <c r="AD8" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
